--- a/data/trans_dic/P15B_3_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P15B_3_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año (tasa de respuesta: 89,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,34; 53,03</t>
+          <t>7,3; 56,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 26,42</t>
+          <t>2,83; 26,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,7</t>
+          <t>0,0; 27,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,76</t>
+          <t>0,0; 34,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,12</t>
+          <t>0,0; 52,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 41,96</t>
+          <t>4,92; 40,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,43</t>
+          <t>0,0; 13,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 36,81</t>
+          <t>4,32; 33,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,89; 29,55</t>
+          <t>6,1; 29,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,82; 27,11</t>
+          <t>4,69; 26,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 21,22</t>
+          <t>1,39; 18,61</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,93; 30,58</t>
+          <t>2,96; 33,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,03</t>
+          <t>0,0; 34,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,23</t>
+          <t>0,0; 26,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,91</t>
+          <t>0,0; 20,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,79</t>
+          <t>0,0; 19,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 17,27</t>
+          <t>1,59; 17,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 21,05</t>
+          <t>2,39; 20,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 16,74</t>
+          <t>1,81; 16,51</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,58; 83,77</t>
+          <t>51,05; 84,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,3; 36,84</t>
+          <t>13,1; 35,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,5; 50,77</t>
+          <t>13,2; 49,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,34; 42,88</t>
+          <t>13,14; 41,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,88</t>
+          <t>0,0; 24,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41,66; 76,17</t>
+          <t>41,43; 75,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,59; 28,58</t>
+          <t>10,73; 29,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,5; 38,95</t>
+          <t>11,49; 39,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,41; 32,81</t>
+          <t>9,87; 34,43</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,3; 48,99</t>
+          <t>17,97; 47,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,96; 33,93</t>
+          <t>16,61; 33,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,54; 28,58</t>
+          <t>9,81; 28,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,05; 39,58</t>
+          <t>16,26; 38,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,87; 51,79</t>
+          <t>13,55; 50,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 24,96</t>
+          <t>4,48; 24,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 23,45</t>
+          <t>2,53; 21,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 27,97</t>
+          <t>5,91; 25,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,73; 46,32</t>
+          <t>21,01; 44,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,3; 27,98</t>
+          <t>14,6; 28,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,01; 21,83</t>
+          <t>8,25; 21,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,51; 30,72</t>
+          <t>13,99; 29,46</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,59; 65,6</t>
+          <t>8,65; 66,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,3; 56,27</t>
+          <t>26,55; 58,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 30,54</t>
+          <t>6,82; 30,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,11; 62,77</t>
+          <t>23,58; 60,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,93</t>
+          <t>0,0; 30,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,04</t>
+          <t>0,0; 11,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,09; 25,82</t>
+          <t>5,22; 28,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,55; 20,72</t>
+          <t>6,33; 20,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 32,45</t>
+          <t>6,13; 34,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,73; 28,88</t>
+          <t>11,74; 29,02</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,83; 24,98</t>
+          <t>7,69; 24,64</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,18; 37,92</t>
+          <t>14,55; 34,16</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,29</t>
+          <t>0,0; 7,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,24</t>
+          <t>0,0; 5,07</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,31</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>23,89; 41,04</t>
+          <t>24,72; 41,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,25; 27,12</t>
+          <t>16,98; 26,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,22; 20,48</t>
+          <t>10,34; 20,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,65; 31,81</t>
+          <t>17,47; 31,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,29; 18,96</t>
+          <t>5,01; 18,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,26</t>
+          <t>2,57; 9,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,25; 11,95</t>
+          <t>4,14; 11,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,73; 11,35</t>
+          <t>4,91; 11,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17,16; 29,1</t>
+          <t>17,46; 28,58</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,11; 17,44</t>
+          <t>10,96; 17,35</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,15; 14,55</t>
+          <t>8,14; 14,7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,63; 19,12</t>
+          <t>11,89; 19,37</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año (tasa de respuesta: 89,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>925; 6681</t>
+          <t>920; 7131</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>955; 8973</t>
+          <t>961; 9019</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6181</t>
+          <t>0; 5937</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 8524</t>
+          <t>0; 8229</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1804</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 9379</t>
+          <t>0; 9138</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>910; 8422</t>
+          <t>988; 8128</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3117</t>
+          <t>0; 3242</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>917; 7495</t>
+          <t>880; 6885</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3019; 15155</t>
+          <t>3131; 15381</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2006; 11278</t>
+          <t>1952; 10981</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>658; 9982</t>
+          <t>656; 8756</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1792</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>923; 9634</t>
+          <t>933; 10606</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5906</t>
+          <t>0; 5844</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6574</t>
+          <t>0; 6378</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1709</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2048</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5722</t>
+          <t>0; 4557</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4815</t>
+          <t>0; 4521</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1884</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>919; 9903</t>
+          <t>911; 10084</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>951; 8198</t>
+          <t>929; 7954</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>814; 7918</t>
+          <t>855; 7812</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14023; 23694</t>
+          <t>14441; 24018</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8551; 22028</t>
+          <t>7834; 21243</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4815; 15773</t>
+          <t>4100; 15443</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3677; 13896</t>
+          <t>4259; 13557</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1516</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1893</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1871</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2745</t>
+          <t>0; 2879</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13849; 25320</t>
+          <t>13772; 25186</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7924; 21381</t>
+          <t>8029; 21829</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4312; 15989</t>
+          <t>4715; 16092</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4179; 14571</t>
+          <t>4385; 15292</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7532; 19117</t>
+          <t>7014; 18717</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17170; 32444</t>
+          <t>15883; 32183</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5037; 16862</t>
+          <t>5790; 16583</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10668; 26314</t>
+          <t>10809; 25682</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3469; 12953</t>
+          <t>3388; 12665</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2122; 12150</t>
+          <t>2183; 11725</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>968; 9020</t>
+          <t>973; 8375</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2891; 13844</t>
+          <t>2928; 12866</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13917; 29656</t>
+          <t>13453; 28720</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22076; 40376</t>
+          <t>21065; 41195</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7804; 21279</t>
+          <t>8041; 21269</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16826; 35639</t>
+          <t>16233; 34170</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1086; 8293</t>
+          <t>1093; 8457</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9542; 22094</t>
+          <t>10422; 22844</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2875; 12453</t>
+          <t>2782; 12382</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8852; 24047</t>
+          <t>9033; 23262</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6718</t>
+          <t>0; 6931</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 7591</t>
+          <t>0; 6670</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2059; 10434</t>
+          <t>2109; 11656</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3480; 11010</t>
+          <t>3365; 10695</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2061; 11388</t>
+          <t>2150; 12102</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11437; 28152</t>
+          <t>11441; 28288</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6360; 20281</t>
+          <t>6243; 20007</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13879; 34670</t>
+          <t>13303; 31232</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1805</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1763</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2013</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3098</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1908</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4774</t>
+          <t>0; 6627</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2181</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 1160</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 1921</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4972</t>
+          <t>0; 5935</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 2157</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 1347</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>29153; 50071</t>
+          <t>30165; 51177</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>49496; 77841</t>
+          <t>48742; 76648</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20213; 40504</t>
+          <t>20451; 40329</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34759; 62641</t>
+          <t>34408; 62141</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4963; 17783</t>
+          <t>4703; 17075</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6941; 23649</t>
+          <t>6561; 23133</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8146; 22882</t>
+          <t>7920; 21957</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9820; 23560</t>
+          <t>10189; 24529</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>37046; 62814</t>
+          <t>37690; 61689</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60244; 94567</t>
+          <t>59450; 94118</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31716; 56626</t>
+          <t>31690; 57225</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>47056; 77360</t>
+          <t>48091; 78353</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15B_3_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P15B_3_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,3; 56,6</t>
+          <t>7,28; 54,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 26,56</t>
+          <t>2,78; 27,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,52</t>
+          <t>0,0; 35,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,73</t>
+          <t>0,0; 51,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 40,5</t>
+          <t>4,51; 39,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,97</t>
+          <t>0,0; 14,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,32; 33,82</t>
+          <t>4,48; 35,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,1; 29,99</t>
+          <t>5,69; 29,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,69; 26,39</t>
+          <t>5,02; 26,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 18,61</t>
+          <t>1,43; 18,91</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 33,67</t>
+          <t>2,92; 34,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,66</t>
+          <t>0,0; 35,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,41</t>
+          <t>0,0; 26,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,63</t>
+          <t>0,0; 22,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,52</t>
+          <t>0,0; 20,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 17,59</t>
+          <t>1,61; 21,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 20,42</t>
+          <t>2,39; 19,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 16,51</t>
+          <t>2,38; 18,29</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51,05; 84,92</t>
+          <t>50,63; 85,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,1; 35,53</t>
+          <t>13,03; 35,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,2; 49,71</t>
+          <t>13,99; 48,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,14; 41,83</t>
+          <t>12,99; 42,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,0</t>
+          <t>0,0; 18,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41,43; 75,76</t>
+          <t>41,48; 75,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,73; 29,18</t>
+          <t>11,09; 28,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,49; 39,2</t>
+          <t>10,7; 37,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,87; 34,43</t>
+          <t>9,96; 32,97</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,97; 47,96</t>
+          <t>19,44; 47,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,61; 33,66</t>
+          <t>16,95; 34,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,81; 28,11</t>
+          <t>8,47; 28,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,26; 38,63</t>
+          <t>15,49; 37,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,55; 50,64</t>
+          <t>15,39; 50,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 24,09</t>
+          <t>6,0; 25,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 21,77</t>
+          <t>2,63; 23,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 25,99</t>
+          <t>5,85; 25,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,01; 44,85</t>
+          <t>21,69; 44,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,6; 28,55</t>
+          <t>15,23; 28,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,25; 21,82</t>
+          <t>8,06; 21,73</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,99; 29,46</t>
+          <t>13,38; 28,56</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,65; 66,9</t>
+          <t>7,92; 61,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,55; 58,18</t>
+          <t>25,93; 57,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,82; 30,36</t>
+          <t>7,09; 32,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,58; 60,72</t>
+          <t>20,81; 60,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,88</t>
+          <t>0,0; 26,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,46</t>
+          <t>0,0; 13,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,22; 28,84</t>
+          <t>5,12; 26,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,33; 20,13</t>
+          <t>6,18; 20,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,13; 34,49</t>
+          <t>5,68; 34,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,74; 29,02</t>
+          <t>11,83; 28,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,69; 24,64</t>
+          <t>8,43; 23,8</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,55; 34,16</t>
+          <t>14,57; 35,84</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,34</t>
+          <t>0,0; 6,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,07</t>
+          <t>0,0; 5,24</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>24,72; 41,94</t>
+          <t>23,7; 41,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,98; 26,71</t>
+          <t>17,04; 26,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,34; 20,39</t>
+          <t>10,14; 20,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,47; 31,56</t>
+          <t>17,14; 30,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,01; 18,2</t>
+          <t>4,76; 18,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 9,06</t>
+          <t>2,74; 9,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,14; 11,47</t>
+          <t>4,23; 11,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,91; 11,81</t>
+          <t>4,71; 11,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17,46; 28,58</t>
+          <t>17,02; 28,57</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,96; 17,35</t>
+          <t>11,15; 17,12</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,14; 14,7</t>
+          <t>8,42; 15,08</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,89; 19,37</t>
+          <t>11,58; 19,07</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>724</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3731</t>
         </is>
       </c>
     </row>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>920; 7131</t>
+          <t>917; 6829</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>961; 9019</t>
+          <t>944; 9357</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 8229</t>
+          <t>0; 9066</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1952,37 +1952,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 9138</t>
+          <t>0; 9004</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>988; 8128</t>
+          <t>904; 7951</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3242</t>
+          <t>0; 3728</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>880; 6885</t>
+          <t>911; 7192</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3131; 15381</t>
+          <t>2921; 15213</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1952; 10981</t>
+          <t>2087; 11020</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>656; 8756</t>
+          <t>742; 9846</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3624</t>
         </is>
       </c>
     </row>
@@ -2140,17 +2140,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>933; 10606</t>
+          <t>920; 10806</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5844</t>
+          <t>0; 5998</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6378</t>
+          <t>0; 6883</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4557</t>
+          <t>0; 5046</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4521</t>
+          <t>0; 5045</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>911; 10084</t>
+          <t>924; 12095</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>929; 7954</t>
+          <t>933; 7518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>855; 7812</t>
+          <t>1205; 9276</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>544</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>9483</t>
         </is>
       </c>
     </row>
@@ -2343,22 +2343,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14441; 24018</t>
+          <t>14321; 24073</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7834; 21243</t>
+          <t>7794; 21007</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4100; 15443</t>
+          <t>4346; 15011</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4259; 13557</t>
+          <t>4697; 15321</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2378,27 +2378,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2879</t>
+          <t>0; 2394</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13772; 25186</t>
+          <t>13790; 25107</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8029; 21829</t>
+          <t>8300; 21391</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4715; 16092</t>
+          <t>4394; 15337</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4385; 15292</t>
+          <t>4863; 16104</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18005</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24818</t>
+          <t>27004</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7014; 18717</t>
+          <t>7585; 18355</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15883; 32183</t>
+          <t>16207; 33058</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5790; 16583</t>
+          <t>4996; 16964</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10809; 25682</t>
+          <t>12051; 28923</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3388; 12665</t>
+          <t>3848; 12652</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2183; 11725</t>
+          <t>2922; 12384</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>973; 8375</t>
+          <t>1011; 9013</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2928; 12866</t>
+          <t>3241; 14334</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13453; 28720</t>
+          <t>13892; 28693</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21065; 41195</t>
+          <t>21974; 40750</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8041; 21269</t>
+          <t>7860; 21177</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16233; 34170</t>
+          <t>17821; 38034</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15459</t>
+          <t>15626</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21821</t>
+          <t>22234</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1093; 8457</t>
+          <t>1001; 7739</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10422; 22844</t>
+          <t>10182; 22684</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2782; 12382</t>
+          <t>2890; 13312</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9033; 23262</t>
+          <t>8392; 24501</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6931</t>
+          <t>0; 5856</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6670</t>
+          <t>0; 7684</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2109; 11656</t>
+          <t>2069; 10862</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3365; 10695</t>
+          <t>3522; 11391</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2150; 12102</t>
+          <t>1995; 12214</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11441; 28288</t>
+          <t>11537; 27970</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6243; 20007</t>
+          <t>6840; 19323</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13303; 31232</t>
+          <t>14175; 34868</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 6627</t>
+          <t>0; 5899</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5935</t>
+          <t>0; 6144</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46487</t>
+          <t>49506</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>62259</t>
+          <t>66076</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>30165; 51177</t>
+          <t>28923; 50647</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>48742; 76648</t>
+          <t>48908; 76630</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20451; 40329</t>
+          <t>20044; 40235</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34408; 62141</t>
+          <t>37208; 65509</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4703; 17075</t>
+          <t>4464; 16998</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6561; 23133</t>
+          <t>7005; 23025</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7920; 21957</t>
+          <t>8102; 22800</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>10189; 24529</t>
+          <t>10620; 26205</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>37690; 61689</t>
+          <t>36733; 61658</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>59450; 94118</t>
+          <t>60449; 92848</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31690; 57225</t>
+          <t>32791; 58691</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>48091; 78353</t>
+          <t>51240; 84363</t>
         </is>
       </c>
     </row>
